--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/phi-4/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4795918367346939</v>
+        <v>0.4897959183673469</v>
       </c>
       <c r="B2">
-        <v>0.03448275862068965</v>
+        <v>0.02777777777777778</v>
       </c>
       <c r="C2">
-        <v>0.4357142857142857</v>
+        <v>0.4014084507042254</v>
       </c>
       <c r="D2">
-        <v>0.6220472440944882</v>
+        <v>0.6343283582089553</v>
       </c>
       <c r="E2">
         <v>98</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
